--- a/output/pdf_financials_xlsx/NDA.xlsx
+++ b/output/pdf_financials_xlsx/NDA.xlsx
@@ -5878,25 +5878,25 @@
         <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.36082</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.412626</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.174587</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>16.70973</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>16.893944</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>17.337013</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>17.571907</v>
       </c>
     </row>
     <row r="93">
@@ -10716,7 +10716,11 @@
           <t>Reserves (Note 9) 17,571,907</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12720,7 +12724,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -14482,7 +14490,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NDA.xlsx
+++ b/output/pdf_financials_xlsx/NDA.xlsx
@@ -1049,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008806</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.008806</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.011321</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1990,13 +1990,13 @@
         <v>-0.008004000000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-22.077103</v>
+        <v>-22.085909</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-22.077103</v>
+        <v>-22.085909</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.361277</v>
+        <v>-4.372598</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0.162945</v>
@@ -2104,13 +2104,13 @@
         <v>-0.008004000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-22.072244</v>
+        <v>-22.08105</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-22.072244</v>
+        <v>-22.08105</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.355655</v>
+        <v>-4.366976</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>0.162945</v>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-5212.897953785402</v>
+        <v>-5214.977705141043</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-5212.897953785402</v>
+        <v>-5214.977705141043</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-2152.950160890905</v>
+        <v>-2158.54600095892</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.062306</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.509996</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.117558</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.154803</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>4.755064</v>
@@ -2492,16 +2492,16 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.062306</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.509996</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.392088</v>
+        <v>0.509646</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>3.327316</v>
+        <v>3.482119</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>6.066164</v>
@@ -3176,16 +3176,16 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.283951</v>
+        <v>0.221645</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.729336</v>
+        <v>0.21934</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.082896</v>
+        <v>0.965338</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>33.582848</v>
+        <v>33.428045</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -55192,7 +55192,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">

--- a/output/pdf_financials_xlsx/NDA.xlsx
+++ b/output/pdf_financials_xlsx/NDA.xlsx
@@ -16762,7 +16762,11 @@
           <t>Share capital - note 7 392,406</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
